--- a/snkrdunk_results.xlsx
+++ b/snkrdunk_results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="50">
   <si>
     <t>Mã sản phẩm</t>
   </si>
@@ -27,12 +27,6 @@
     <t>Giá tiền (¥)</t>
   </si>
   <si>
-    <t>Số sản phẩm hiện có</t>
-  </si>
-  <si>
-    <t>Thời gian quét</t>
-  </si>
-  <si>
     <t>SUP-FW26-WEEK1-001</t>
   </si>
   <si>
@@ -42,9 +36,6 @@
     <t>S</t>
   </si>
   <si>
-    <t>Mon Sep 07 2026 21:18:28 GMT+0700 (Indochina Time)</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -93,10 +84,85 @@
     <t>Supreme Baggy Jean "Dirty Indigo"</t>
   </si>
   <si>
+    <t>Supreme Baggy Jean "Black"</t>
+  </si>
+  <si>
+    <t>Supreme Baggy Jean "Khaki"</t>
+  </si>
+  <si>
+    <t>Supreme Baggy Jean "Light Washed Indigo"</t>
+  </si>
+  <si>
+    <t>Supreme Baggy Jean "Burgundy"</t>
+  </si>
+  <si>
     <t>CW2288-111</t>
   </si>
   <si>
-    <t>Nike Air Force 1 Low '07 White/White</t>
+    <t>Nike Air Force 1 Low '07 "White/White"</t>
+  </si>
+  <si>
+    <t>22cm</t>
+  </si>
+  <si>
+    <t>22.5cm</t>
+  </si>
+  <si>
+    <t>23cm</t>
+  </si>
+  <si>
+    <t>23.5cm</t>
+  </si>
+  <si>
+    <t>24cm</t>
+  </si>
+  <si>
+    <t>24.5cm</t>
+  </si>
+  <si>
+    <t>25cm</t>
+  </si>
+  <si>
+    <t>25.5cm</t>
+  </si>
+  <si>
+    <t>26cm</t>
+  </si>
+  <si>
+    <t>26.5cm</t>
+  </si>
+  <si>
+    <t>27cm</t>
+  </si>
+  <si>
+    <t>27.5cm</t>
+  </si>
+  <si>
+    <t>28cm</t>
+  </si>
+  <si>
+    <t>28.5cm</t>
+  </si>
+  <si>
+    <t>29cm</t>
+  </si>
+  <si>
+    <t>29.5cm</t>
+  </si>
+  <si>
+    <t>30cm</t>
+  </si>
+  <si>
+    <t>30.5cm</t>
+  </si>
+  <si>
+    <t>31cm</t>
+  </si>
+  <si>
+    <t>31.5cm</t>
+  </si>
+  <si>
+    <t>32cm</t>
   </si>
 </sst>
 </file>
@@ -499,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -524,882 +590,1316 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2">
         <v>10500</v>
       </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
       <c r="D3">
         <v>13300</v>
       </c>
-      <c r="E3">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>11390</v>
       </c>
-      <c r="E4">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>10850</v>
       </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>12879</v>
       </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
       </c>
       <c r="D7">
         <v>10998</v>
       </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>13298</v>
       </c>
-      <c r="E8">
-        <v>48</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>12980</v>
       </c>
-      <c r="E9">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>11698</v>
       </c>
-      <c r="E10">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>10799</v>
       </c>
-      <c r="E11">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
         <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
       </c>
       <c r="D12">
         <v>11499</v>
       </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>11500</v>
       </c>
-      <c r="E13">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>11899</v>
       </c>
-      <c r="E14">
-        <v>16</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15">
         <v>10495</v>
       </c>
-      <c r="E15">
-        <v>13</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>13599</v>
       </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
       </c>
       <c r="D17">
         <v>13888</v>
       </c>
-      <c r="E17">
-        <v>13</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F17" s="2"/>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>14999</v>
       </c>
-      <c r="E18">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>12900</v>
       </c>
-      <c r="E19">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>13998</v>
       </c>
-      <c r="E20">
-        <v>8</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F20" s="2"/>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>13480</v>
       </c>
-      <c r="E21">
-        <v>8</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
         <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
       </c>
       <c r="D22">
         <v>11400</v>
       </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>11700</v>
       </c>
-      <c r="E23">
-        <v>15</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>12800</v>
       </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F24" s="2"/>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25">
         <v>12450</v>
       </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>12900</v>
       </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F26" s="2"/>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
         <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
       </c>
       <c r="D27">
         <v>10899</v>
       </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>11999</v>
       </c>
-      <c r="E28">
-        <v>9</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F28" s="2"/>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>11099</v>
       </c>
-      <c r="E29">
-        <v>6</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F29" s="2"/>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30">
         <v>11000</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F30" s="2"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>11000</v>
       </c>
-      <c r="E31">
-        <v>3</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F31" s="2"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D32" s="3">
         <v>36940</v>
       </c>
-      <c r="E32" s="3">
-        <v>9</v>
-      </c>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="3">
         <v>36940</v>
       </c>
-      <c r="E33" s="3">
-        <v>11</v>
-      </c>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3">
         <v>36952</v>
       </c>
-      <c r="E34" s="3">
-        <v>13</v>
-      </c>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="3">
         <v>33998</v>
       </c>
-      <c r="E35" s="3">
-        <v>11</v>
-      </c>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D36" s="3">
         <v>36950</v>
       </c>
-      <c r="E36" s="3">
-        <v>6</v>
-      </c>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D37" s="3">
         <v>36944</v>
       </c>
-      <c r="E37" s="3">
-        <v>8</v>
-      </c>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38" s="3">
         <v>36934</v>
       </c>
-      <c r="E38" s="3">
-        <v>9</v>
-      </c>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D39" s="3">
         <v>36940</v>
       </c>
-      <c r="E39" s="3">
-        <v>10</v>
-      </c>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="3">
         <v>35882</v>
       </c>
-      <c r="E40" s="3">
-        <v>9</v>
-      </c>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C41" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D41" s="3">
         <v>36883</v>
       </c>
-      <c r="E41" s="3">
-        <v>9</v>
-      </c>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D42" s="3">
         <v>36965</v>
       </c>
-      <c r="E42" s="3">
-        <v>6</v>
-      </c>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D43" s="3">
         <v>36955</v>
       </c>
-      <c r="E43" s="3">
-        <v>8</v>
-      </c>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" s="3">
         <v>36960</v>
       </c>
-      <c r="E44" s="3">
-        <v>8</v>
-      </c>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D45" s="3">
         <v>36958</v>
       </c>
-      <c r="E45" s="3">
-        <v>8</v>
-      </c>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D46" s="3">
         <v>36958</v>
       </c>
-      <c r="E46" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="3">
+        <v>30</v>
+      </c>
+      <c r="D47" s="3">
+        <v>33489</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="3">
+        <v>32</v>
+      </c>
+      <c r="D48" s="3">
+        <v>33980</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="3">
+        <v>34</v>
+      </c>
+      <c r="D49" s="3">
+        <v>31900</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="3">
+        <v>36</v>
+      </c>
+      <c r="D50" s="3">
+        <v>34799</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="3">
+        <v>37</v>
+      </c>
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="3">
+        <v>30</v>
+      </c>
+      <c r="D52" s="3">
+        <v>34800</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53" s="3">
+        <v>32</v>
+      </c>
+      <c r="D53" s="3">
+        <v>35499</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="3">
+        <v>34</v>
+      </c>
+      <c r="D54" s="3">
+        <v>33900</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" s="3">
+        <v>36</v>
+      </c>
+      <c r="D55" s="3">
+        <v>39589</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" s="3">
+        <v>38</v>
+      </c>
+      <c r="D56" s="3">
+        <v>44990</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C57" s="3">
+        <v>30</v>
+      </c>
+      <c r="D57" s="3">
+        <v>32896</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="3">
+        <v>32</v>
+      </c>
+      <c r="D58" s="3">
+        <v>34800</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="3">
+        <v>34</v>
+      </c>
+      <c r="D59" s="3">
+        <v>35999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="3">
+        <v>36</v>
+      </c>
+      <c r="D60" s="3">
+        <v>57999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="3">
+        <v>38</v>
+      </c>
+      <c r="D61" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="C62" s="3">
+        <v>30</v>
+      </c>
+      <c r="D62" s="3">
+        <v>30900</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" s="3">
+        <v>32</v>
+      </c>
+      <c r="D63" s="3">
+        <v>38770</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="3">
+        <v>34</v>
+      </c>
+      <c r="D64" s="3">
+        <v>29500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" s="3">
+        <v>36</v>
+      </c>
+      <c r="D65" s="3">
+        <v>34999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="3">
+        <v>38</v>
+      </c>
+      <c r="D66" s="3">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B48" t="s">
-        <v>27</v>
+      <c r="C67" s="3">
+        <v>30</v>
+      </c>
+      <c r="D67" s="3">
+        <v>36499</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="3">
+        <v>32</v>
+      </c>
+      <c r="D68" s="3">
+        <v>40999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="3">
+        <v>34</v>
+      </c>
+      <c r="D69" s="3">
+        <v>40999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" s="3">
+        <v>36</v>
+      </c>
+      <c r="D70" s="3">
+        <v>55555</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="3">
+        <v>38</v>
+      </c>
+      <c r="D71" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" s="3"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" s="3"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" s="3">
+        <v>16350</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="3">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="3">
+        <v>13937</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D79" s="3">
+        <v>14999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" s="3">
+        <v>13751</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="3">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D82" s="3">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="3">
+        <v>13499</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="3">
+        <v>13708</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D85" s="3">
+        <v>14421</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86" s="3">
+        <v>13699</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" s="3">
+        <v>16575</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D89" s="3">
+        <v>16995</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92" s="3">
+        <v>16995</v>
       </c>
     </row>
   </sheetData>
